--- a/results/modelling/global/metrics_summary_all_models.xlsx
+++ b/results/modelling/global/metrics_summary_all_models.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,32 +479,311 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>parametric_fold</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.6170804183178902</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2.105366262903306</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.07226047152708</v>
+      </c>
+      <c r="E2" t="n">
+        <v>6.006018687244245</v>
+      </c>
+      <c r="F2" t="n">
+        <v>570.6301770647091</v>
+      </c>
+      <c r="G2" t="n">
+        <v>25.37145820457359</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1831.104177633461</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1881.775092850317</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>global_qP_global</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.9280406073341938</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.7726756331322739</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6.778807038833483</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2.603614226192791</v>
+      </c>
+      <c r="F3" t="n">
+        <v>16.98606219421146</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4.77275274498318</v>
+      </c>
+      <c r="H3" t="n">
+        <v>988.5557712821609</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1039.226686499017</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>global_rP_global</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.9279658290751694</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.7776058356817663</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6.785851392181209</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2.604966677748721</v>
+      </c>
+      <c r="F4" t="n">
+        <v>17.58473193292106</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4.777706225804295</v>
+      </c>
+      <c r="H4" t="n">
+        <v>989.0792425401324</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1039.750157756989</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>global_P_fold</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>0.9278452922655742</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.7871840765505587</v>
-      </c>
-      <c r="D2" t="n">
-        <v>6.797206348678928</v>
-      </c>
-      <c r="E2" t="n">
-        <v>2.60714524886492</v>
-      </c>
-      <c r="F2" t="n">
-        <v>23.34934670224594</v>
-      </c>
-      <c r="G2" t="n">
-        <v>4.785690856395577</v>
-      </c>
-      <c r="H2" t="n">
-        <v>989.9218951323775</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1040.592810349234</v>
+      <c r="B5" t="n">
+        <v>0.92796306777117</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.7874850581396673</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6.786111515930099</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2.605016605691814</v>
+      </c>
+      <c r="F5" t="n">
+        <v>23.12457196682151</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4.777889140819718</v>
+      </c>
+      <c r="H5" t="n">
+        <v>989.0985621286612</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1039.769477345518</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>global_ind_qP_global</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.9280589786605395</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.7720935013720499</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6.777076400598053</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2.603281851931913</v>
+      </c>
+      <c r="F6" t="n">
+        <v>18.54315620118627</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4.771535786820476</v>
+      </c>
+      <c r="H6" t="n">
+        <v>988.4270830001625</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1039.097998217019</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>global_ind_rP_global</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.9280140732649141</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.7827351495147533</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6.781306633798614</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2.604094206014563</v>
+      </c>
+      <c r="F7" t="n">
+        <v>22.24163844758006</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4.774510421679556</v>
+      </c>
+      <c r="H7" t="n">
+        <v>988.7415803258177</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1039.412495542674</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>global_ind_P_fold</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.9279532716030739</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.7858158431132962</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6.787034346581978</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2.605193725345963</v>
+      </c>
+      <c r="F8" t="n">
+        <v>22.34570947039661</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4.778538061126462</v>
+      </c>
+      <c r="H8" t="n">
+        <v>989.1670954891622</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1039.838010706019</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>induction_qP_global</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.9276391850624346</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.8076510890761722</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6.816622312427905</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.610866199641013</v>
+      </c>
+      <c r="F9" t="n">
+        <v>32.2373765478484</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4.799343863180803</v>
+      </c>
+      <c r="H9" t="n">
+        <v>991.3594998808808</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1042.030415097737</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>induction_rP_global</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.9280124657775572</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.7827132519271389</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6.781458064295815</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.60412328131673</v>
+      </c>
+      <c r="F10" t="n">
+        <v>22.21314465309812</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4.774616905273803</v>
+      </c>
+      <c r="H10" t="n">
+        <v>988.7528348115059</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1039.423750028362</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>induction_P_fold</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.9278060386059956</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.7926221705112618</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6.800904170102839</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.607854323021675</v>
+      </c>
+      <c r="F11" t="n">
+        <v>22.71078141588476</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4.788291107490189</v>
+      </c>
+      <c r="H11" t="n">
+        <v>990.1960070453549</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1040.866922262211</v>
       </c>
     </row>
   </sheetData>
@@ -518,7 +797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -576,7 +855,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>global_P_fold</t>
+          <t>parametric_fold</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -585,34 +864,34 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.8005465547938748</v>
+        <v>-135.6591363296641</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1492902187498827</v>
+        <v>4.648006464514677</v>
       </c>
       <c r="E2" t="n">
-        <v>0.09287839281289882</v>
+        <v>63.63731111478562</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3047595655806374</v>
+        <v>7.977299738306542</v>
       </c>
       <c r="G2" t="n">
-        <v>30.13402441666043</v>
+        <v>1045.380126509084</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1308509085308667</v>
+        <v>171.0997173584983</v>
       </c>
       <c r="I2" t="n">
-        <v>-16.39989217607675</v>
+        <v>94.60439916837404</v>
       </c>
       <c r="J2" t="n">
-        <v>-6.401332047402157</v>
+        <v>104.6029592970486</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>global_P_fold</t>
+          <t>parametric_fold</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -621,34 +900,34 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9584156672460971</v>
+        <v>-67.00241232875298</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07213629115672146</v>
+        <v>3.022412975155626</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01651818546309257</v>
+        <v>27.0120111204287</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1285230931120651</v>
+        <v>5.197308064799382</v>
       </c>
       <c r="G3" t="n">
-        <v>33.47809911998309</v>
+        <v>1101.547105775528</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03003802965033568</v>
+        <v>78.63026296585198</v>
       </c>
       <c r="I3" t="n">
-        <v>-37.54940033576815</v>
+        <v>73.44422435095905</v>
       </c>
       <c r="J3" t="n">
-        <v>-29.05279792254163</v>
+        <v>81.94082676418556</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>global_P_fold</t>
+          <t>parametric_fold</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -657,34 +936,34 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.9717913157995759</v>
+        <v>-3264.481482321026</v>
       </c>
       <c r="D4" t="n">
-        <v>0.008742817522964443</v>
+        <v>3.457856389600832</v>
       </c>
       <c r="E4" t="n">
-        <v>0.000370310578062508</v>
+        <v>42.86773274424948</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01924345546055874</v>
+        <v>6.547345473109654</v>
       </c>
       <c r="G4" t="n">
-        <v>16.28639062043155</v>
+        <v>6033.091559173914</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01472182266477099</v>
+        <v>2019.315715234565</v>
       </c>
       <c r="I4" t="n">
-        <v>-141.9245385893836</v>
+        <v>102.9205072413069</v>
       </c>
       <c r="J4" t="n">
-        <v>-129.3902693367026</v>
+        <v>115.4547764939879</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>global_P_fold</t>
+          <t>parametric_fold</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -693,34 +972,34 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.09440684190958415</v>
+        <v>-2881.917784130143</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03441064619329541</v>
+        <v>2.090270522989905</v>
       </c>
       <c r="E5" t="n">
-        <v>0.006089598856466664</v>
+        <v>19.38598219817107</v>
       </c>
       <c r="F5" t="n">
-        <v>0.07803588185230345</v>
+        <v>4.402951532571199</v>
       </c>
       <c r="G5" t="n">
-        <v>68.21298670007528</v>
+        <v>4089.976162178394</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2819406666266515</v>
+        <v>1756.903045555525</v>
       </c>
       <c r="I5" t="n">
-        <v>-83.12463444158909</v>
+        <v>86.25555499353264</v>
       </c>
       <c r="J5" t="n">
-        <v>-70.59036518890801</v>
+        <v>98.78982424621373</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>global_P_fold</t>
+          <t>parametric_fold</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -729,64 +1008,2008 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-5.435308422855499</v>
+        <v>-8495.226043522336</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1773619993845482</v>
+        <v>10.59477225766001</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2743182405653318</v>
+        <v>362.1690875649164</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5237539885913346</v>
+        <v>19.03074059423113</v>
       </c>
       <c r="G6" t="n">
-        <v>101.5010899848057</v>
+        <v>5541.195198481908</v>
       </c>
       <c r="H6" t="n">
-        <v>4.257230590504764</v>
+        <v>5604.784348704286</v>
       </c>
       <c r="I6" t="n">
-        <v>-10.92359238560066</v>
+        <v>183.0870022783026</v>
       </c>
       <c r="J6" t="n">
-        <v>4.626450006451293</v>
+        <v>198.6370446703545</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>parametric_fold</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BR08</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>-2321.117397437931</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5.967356041367196</v>
+      </c>
+      <c r="E7" t="n">
+        <v>87.69614757039496</v>
+      </c>
+      <c r="F7" t="n">
+        <v>9.364622126407181</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3240.0904659053</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1516.057045061312</v>
+      </c>
+      <c r="I7" t="n">
+        <v>135.8469492762947</v>
+      </c>
+      <c r="J7" t="n">
+        <v>150.473459174713</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>global_qP_global</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BR02</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.9492173748221677</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.08554450998674656</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.02364766677488337</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1537779788359939</v>
+      </c>
+      <c r="G8" t="n">
+        <v>18.15790677115524</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.03778815429576805</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-39.65634403119135</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-29.65778390251675</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>global_qP_global</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BR03</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.8404511952855884</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.1187483404733263</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0633761941614906</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2517462892705483</v>
+      </c>
+      <c r="G9" t="n">
+        <v>32.68656403648551</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.09822797732736691</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-17.38000461695177</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-8.883402203725254</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>global_qP_global</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BR04</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.9154276105767704</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.01755397322903035</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.001110227268770403</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.03332007306070026</v>
+      </c>
+      <c r="G10" t="n">
+        <v>33.05813342771476</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.03214887591510818</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-118.8670012974881</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-106.332732044807</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>global_qP_global</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>BR05</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.9821615565055554</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.005758768742016479</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.0001199533853965686</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.01095232328762115</v>
+      </c>
+      <c r="G11" t="n">
+        <v>14.011728759742</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.01143550041811099</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-165.5965542592595</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-153.0622850065784</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>global_qP_global</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BR07</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.9816066125563733</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.01519985788593048</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.0007840559224251261</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.02800099859692733</v>
+      </c>
+      <c r="G12" t="n">
+        <v>10.68335084178645</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.01206685537878561</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-169.0778156844131</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-153.5277732923611</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>global_qP_global</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BR08</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.9879926389243883</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.01176795089016557</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.000453465147791266</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.02129472112499401</v>
+      </c>
+      <c r="G13" t="n">
+        <v>16.45291755149852</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.009919633926137407</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-168.4648035745064</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-153.838293676088</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>global_rP_global</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>BR02</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0.8485279139307744</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.1319014827234317</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.07053517624419914</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.2655845933863618</v>
+      </c>
+      <c r="G14" t="n">
+        <v>21.24872180965945</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.1008162491917071</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-21.0779435762864</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-11.0793834476118</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>global_rP_global</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>BR03</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0.3833119605901091</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.219859429584279</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.2449616654456825</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.4949360215681241</v>
+      </c>
+      <c r="G15" t="n">
+        <v>50.18302484093834</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.3624795776349451</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.900196776274303</v>
+      </c>
+      <c r="J15" t="n">
+        <v>11.39679918950082</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>global_rP_global</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>BR04</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.8177632614894389</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.02596456897221756</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.002392319737517474</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.0489113456931771</v>
+      </c>
+      <c r="G16" t="n">
+        <v>49.4690888819636</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.06234564536943057</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-102.7453274282162</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-90.21105817553516</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>global_rP_global</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>BR05</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.988308752471203</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.004681203230994409</v>
+      </c>
+      <c r="E17" t="n">
+        <v>7.861698925835162e-05</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.008866622201173997</v>
+      </c>
+      <c r="G17" t="n">
+        <v>11.60240256008975</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.009562406151119954</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-174.469377404775</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-161.9351081520939</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>global_rP_global</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BR07</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.9777447102066457</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.01659403622860814</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.0009486774429803627</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.03080060783459253</v>
+      </c>
+      <c r="G18" t="n">
+        <v>10.94804636657624</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.01334066114809256</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-163.9319261326304</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-148.3818837405785</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>global_rP_global</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BR08</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.9890693161137679</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.01130598102735859</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.0004128037920003453</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.02031757347717353</v>
+      </c>
+      <c r="G19" t="n">
+        <v>15.78022444016893</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.009568167820269868</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-170.8134539447941</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-156.1869440463757</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>global_P_fold</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>BR02</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.6073303751521468</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.2283008841795378</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.1828523123509953</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.4276123388666367</v>
+      </c>
+      <c r="G20" t="n">
+        <v>54.40532814377115</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.2517975061000526</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-4.884300301154614</v>
+      </c>
+      <c r="J20" t="n">
+        <v>5.114259827519984</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>global_P_fold</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>BR03</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.9063456772150384</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.0897593192099128</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.03720149803382704</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.1928768986525526</v>
+      </c>
+      <c r="G21" t="n">
+        <v>26.18325774759989</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.06013734545916739</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-25.3710937318096</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-16.87449131858308</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>global_P_fold</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>BR04</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0.9641675638716671</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.01172495433638124</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.0004703916723585195</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.02168851475685966</v>
+      </c>
+      <c r="G22" t="n">
+        <v>21.98109466612958</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.01707900500915083</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-136.9008421619768</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-124.3665729092957</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>global_P_fold</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>BR05</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0.7112695284327581</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.02647791321291858</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.001941548181735942</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.04406300241399742</v>
+      </c>
+      <c r="G23" t="n">
+        <v>64.14814689420729</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.09397822519738773</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-107.1296614391891</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-94.59539218650798</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>global_P_fold</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>BR07</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.3463106845898629</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.08940744106400159</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.02786484984042101</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.1669276784731071</v>
+      </c>
+      <c r="G24" t="n">
+        <v>53.15665304553558</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.2216121895113358</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-72.67050966357553</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-57.12046727152358</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>global_P_fold</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
         <is>
           <t>BR08</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>-0.3931082103874284</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.09707699824374214</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.05261156190227901</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.229372103583411</v>
-      </c>
-      <c r="G7" t="n">
-        <v>66.6167655885034</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.9215211128956478</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-49.620484384115</v>
-      </c>
-      <c r="J7" t="n">
-        <v>-34.9939744856966</v>
+      <c r="C25" t="n">
+        <v>0.3402080224833306</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.1379931415225295</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.02491743728801341</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.1578525808721967</v>
+      </c>
+      <c r="G25" t="n">
+        <v>94.49535701683655</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.2213797993566102</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-68.3046856977671</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-53.67817579934869</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>global_ind_qP_global</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>BR02</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.9958241535455704</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.02798856055435583</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.001944543534557873</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.04409697874637074</v>
+      </c>
+      <c r="G26" t="n">
+        <v>14.80477021707731</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.008613934410519388</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-82.12637627297875</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-72.12781614430415</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>global_ind_qP_global</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BR03</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.9850187497845564</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.04027540788310947</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.005950872675826841</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.07714189961251175</v>
+      </c>
+      <c r="G27" t="n">
+        <v>20.67325629683002</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.01465998593771187</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-52.86326102959704</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-44.36665861637052</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>global_ind_qP_global</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>BR04</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.9783962967836752</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.007866928860550676</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.0002836034381996378</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.01684052962942786</v>
+      </c>
+      <c r="G28" t="n">
+        <v>18.13821325768107</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.01267963337163718</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-147.526606439324</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-134.9923371866429</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>global_ind_qP_global</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>BR05</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.9402673302427061</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.01049836218812276</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.0004016682261764622</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.02004166226081215</v>
+      </c>
+      <c r="G29" t="n">
+        <v>28.09948012714894</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.02420096868551169</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-140.2175664804815</v>
+      </c>
+      <c r="J29" t="n">
+        <v>-127.6832972278004</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>global_ind_qP_global</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>BR07</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.9774666981486664</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.01965699137212053</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.0009605282780281379</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.03099239064719174</v>
+      </c>
+      <c r="G30" t="n">
+        <v>15.87098348203059</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.01343236035001978</v>
+      </c>
+      <c r="I30" t="n">
+        <v>-163.596732651576</v>
+      </c>
+      <c r="J30" t="n">
+        <v>-148.046690259524</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>global_ind_qP_global</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>BR08</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.6016416101951607</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.08559613403744323</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.01504424202530608</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.1226549714659218</v>
+      </c>
+      <c r="G31" t="n">
+        <v>57.65079950440185</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.1360384863591661</v>
+      </c>
+      <c r="I31" t="n">
+        <v>-80.91899876685041</v>
+      </c>
+      <c r="J31" t="n">
+        <v>-66.292488868432</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>global_ind_rP_global</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>BR02</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.942480770334623</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.09779218834126532</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.02678466446962219</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.1636602104044297</v>
+      </c>
+      <c r="G32" t="n">
+        <v>27.87667178736398</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.04200503402834865</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-37.53873820099573</v>
+      </c>
+      <c r="J32" t="n">
+        <v>-27.54017807232113</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>global_ind_rP_global</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>BR03</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.9036227460136417</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.1101547893929558</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.03828310448532633</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.195660687122698</v>
+      </c>
+      <c r="G33" t="n">
+        <v>43.74061146977564</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.06171134933563593</v>
+      </c>
+      <c r="I33" t="n">
+        <v>-24.94119924417111</v>
+      </c>
+      <c r="J33" t="n">
+        <v>-16.44459683094459</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>global_ind_rP_global</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BR04</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.7549856722491133</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.02976845441713929</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.003216434935368715</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.05671362213233003</v>
+      </c>
+      <c r="G34" t="n">
+        <v>55.28776858508739</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.08175580278002413</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-96.5291156099611</v>
+      </c>
+      <c r="J34" t="n">
+        <v>-83.99484635728001</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>global_ind_rP_global</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BR05</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.4517496294332493</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.03109105393290582</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.003686671878905005</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.06071796998339952</v>
+      </c>
+      <c r="G35" t="n">
+        <v>70.48143675492847</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.1730557814852588</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-93.663654312733</v>
+      </c>
+      <c r="J35" t="n">
+        <v>-81.12938506005193</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>global_ind_rP_global</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BR07</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.8061014216803246</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.05537383712791812</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.008265325196204184</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.09091383390994015</v>
+      </c>
+      <c r="G36" t="n">
+        <v>37.48765349370173</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.06995530113324556</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-105.4835274620996</v>
+      </c>
+      <c r="J36" t="n">
+        <v>-89.93348507004768</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>global_ind_rP_global</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>BR08</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>-0.3483953177459476</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.1364683285376958</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.05092295286136107</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.2256611461048647</v>
+      </c>
+      <c r="G37" t="n">
+        <v>77.80710050469769</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.8923293246534741</v>
+      </c>
+      <c r="I37" t="n">
+        <v>-50.43603791917234</v>
+      </c>
+      <c r="J37" t="n">
+        <v>-35.80952802075393</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>global_ind_P_fold</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>BR02</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.7143759036629604</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.1541016707379723</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.1330050077049567</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.3646985161814573</v>
+      </c>
+      <c r="G38" t="n">
+        <v>29.38175095621351</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.1847907342945815</v>
+      </c>
+      <c r="I38" t="n">
+        <v>-10.29526449238794</v>
+      </c>
+      <c r="J38" t="n">
+        <v>-0.2967043637133386</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>global_ind_P_fold</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>BR03</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.9357590505026809</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.07464108127115485</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.02551787771615221</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.1597431617195309</v>
+      </c>
+      <c r="G39" t="n">
+        <v>25.34967087143018</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.04313479925050227</v>
+      </c>
+      <c r="I39" t="n">
+        <v>-31.0256397833467</v>
+      </c>
+      <c r="J39" t="n">
+        <v>-22.52903737012019</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>global_ind_P_fold</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>BR04</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.9489093458003982</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.01020567355451904</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.0006706945122226501</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.02589777041026216</v>
+      </c>
+      <c r="G40" t="n">
+        <v>16.0075324138305</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.02179668241843639</v>
+      </c>
+      <c r="I40" t="n">
+        <v>-129.4511327381758</v>
+      </c>
+      <c r="J40" t="n">
+        <v>-116.9168634854947</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>global_ind_P_fold</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>BR05</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>-0.1061125155919211</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.04125598283481639</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.007437977473543939</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.08624370976218462</v>
+      </c>
+      <c r="G41" t="n">
+        <v>84.34546561333883</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.6860806778181142</v>
+      </c>
+      <c r="I41" t="n">
+        <v>-78.92428255299635</v>
+      </c>
+      <c r="J41" t="n">
+        <v>-66.39001330031527</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>global_ind_P_fold</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>BR07</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.05529769846160315</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.0912661401784936</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.04026987615630736</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.2006735561958958</v>
+      </c>
+      <c r="G42" t="n">
+        <v>50.47121902571124</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.3175996037709343</v>
+      </c>
+      <c r="I42" t="n">
+        <v>-62.72809264534753</v>
+      </c>
+      <c r="J42" t="n">
+        <v>-47.17805025329558</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>global_ind_P_fold</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>BR08</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>-0.754119254784154</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.1507233968251267</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.06624535916803671</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.25738173821784</v>
+      </c>
+      <c r="G43" t="n">
+        <v>86.24485387074829</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1.157215055705744</v>
+      </c>
+      <c r="I43" t="n">
+        <v>-43.85974667158068</v>
+      </c>
+      <c r="J43" t="n">
+        <v>-29.23323677316228</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>induction_qP_global</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>BR02</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.4233650413754192</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.3127000696595981</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.2685184411902992</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.5181876505574976</v>
+      </c>
+      <c r="G44" t="n">
+        <v>82.83084249974198</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.3669533964205837</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1.647793352981392</v>
+      </c>
+      <c r="J44" t="n">
+        <v>11.64635348165599</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>induction_qP_global</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>BR03</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>-0.6268942863405074</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.4324432358406863</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.6462371708512237</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.8038887801501049</v>
+      </c>
+      <c r="G45" t="n">
+        <v>139.0873590754149</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1.892868610996018</v>
+      </c>
+      <c r="I45" t="n">
+        <v>17.45116942443844</v>
+      </c>
+      <c r="J45" t="n">
+        <v>25.94777183766496</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>induction_qP_global</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>BR04</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>-17.75539577796259</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.2651263845329371</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.2462121736335374</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.4961977162719891</v>
+      </c>
+      <c r="G46" t="n">
+        <v>493.4171585079131</v>
+      </c>
+      <c r="H46" t="n">
+        <v>11.60993450986451</v>
+      </c>
+      <c r="I46" t="n">
+        <v>-5.432794027121176</v>
+      </c>
+      <c r="J46" t="n">
+        <v>7.101475225559902</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>induction_qP_global</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>BR05</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.8714327281533696</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.01486866392062623</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.0008645417698022307</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.02940309116066252</v>
+      </c>
+      <c r="G47" t="n">
+        <v>34.99271128998283</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.04517536079285069</v>
+      </c>
+      <c r="I47" t="n">
+        <v>-124.1195296831047</v>
+      </c>
+      <c r="J47" t="n">
+        <v>-111.5852604304236</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>induction_qP_global</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>BR07</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.3232122409296073</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.1021986447853731</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.02884946844893631</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.1698513127677743</v>
+      </c>
+      <c r="G48" t="n">
+        <v>65.14800806952728</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.2292309556353732</v>
+      </c>
+      <c r="I48" t="n">
+        <v>-71.73292019280652</v>
+      </c>
+      <c r="J48" t="n">
+        <v>-56.18287780075457</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>induction_qP_global</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>BR08</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.7415923234793511</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.06461859689114323</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.009758919923032634</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.09878724575081864</v>
+      </c>
+      <c r="G49" t="n">
+        <v>55.04843430658151</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.09035354690231753</v>
+      </c>
+      <c r="I49" t="n">
+        <v>-91.73933870761279</v>
+      </c>
+      <c r="J49" t="n">
+        <v>-77.11282880919438</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>induction_rP_global</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>BR02</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.9414505858506642</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.09843301642931242</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.0272643848327976</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.1651193048459131</v>
+      </c>
+      <c r="G50" t="n">
+        <v>27.62974601975025</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.04264989362775905</v>
+      </c>
+      <c r="I50" t="n">
+        <v>-37.23695822749603</v>
+      </c>
+      <c r="J50" t="n">
+        <v>-27.23839809882143</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>induction_rP_global</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>BR03</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0.9090737847592535</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.1060456855431119</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.03611783542836233</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.1900469295420537</v>
+      </c>
+      <c r="G51" t="n">
+        <v>42.80516230744533</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.05856034937207758</v>
+      </c>
+      <c r="I51" t="n">
+        <v>-25.81452719192332</v>
+      </c>
+      <c r="J51" t="n">
+        <v>-17.3179247786968</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>induction_rP_global</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>BR04</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.7869683992505639</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.0274949305475261</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.002796580466447951</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.05288270479512135</v>
+      </c>
+      <c r="G52" t="n">
+        <v>52.26240803301273</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.0718670865513444</v>
+      </c>
+      <c r="I52" t="n">
+        <v>-99.46651527277176</v>
+      </c>
+      <c r="J52" t="n">
+        <v>-86.93224602009067</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>induction_rP_global</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>BR05</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0.5047725476255526</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.02945417730549118</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.003330122915271892</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.0577072171853044</v>
+      </c>
+      <c r="G53" t="n">
+        <v>67.50433929176376</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.1568993217530246</v>
+      </c>
+      <c r="I53" t="n">
+        <v>-95.79966734773667</v>
+      </c>
+      <c r="J53" t="n">
+        <v>-83.26539809505559</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>induction_rP_global</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>BR07</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0.8244859104919592</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.05323417232392352</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.007481648596246778</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.0864965236078698</v>
+      </c>
+      <c r="G54" t="n">
+        <v>36.3684899105393</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.06389138086978499</v>
+      </c>
+      <c r="I54" t="n">
+        <v>-108.1731569892412</v>
+      </c>
+      <c r="J54" t="n">
+        <v>-92.62311459718927</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>induction_rP_global</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>BR08</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>-0.4946752146282869</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.1436521470797448</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.05644730035461423</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.2375864060812702</v>
+      </c>
+      <c r="G55" t="n">
+        <v>81.25457401305202</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.9878313492734322</v>
+      </c>
+      <c r="I55" t="n">
+        <v>-47.86119532965336</v>
+      </c>
+      <c r="J55" t="n">
+        <v>-33.23468543123495</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>induction_P_fold</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>BR02</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0.07857686751760085</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.3333337353130066</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.4290740606518431</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.6550374498086678</v>
+      </c>
+      <c r="G56" t="n">
+        <v>55.21890071551628</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.5827787822010099</v>
+      </c>
+      <c r="I56" t="n">
+        <v>9.615862430168713</v>
+      </c>
+      <c r="J56" t="n">
+        <v>19.61442255884331</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>induction_P_fold</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>BR03</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0.462120720638594</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0.1677181877507518</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.2136571421219302</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.4622306157341054</v>
+      </c>
+      <c r="G57" t="n">
+        <v>29.14891464495499</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.316923783293773</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.8492596743663299</v>
+      </c>
+      <c r="J57" t="n">
+        <v>9.345862087592849</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>induction_P_fold</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>BR04</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.8963766886448536</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.01849844643236161</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.001360318973264927</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.0368825022641486</v>
+      </c>
+      <c r="G58" t="n">
+        <v>34.90224278706977</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.03803921668782936</v>
+      </c>
+      <c r="I58" t="n">
+        <v>-114.6007574189448</v>
+      </c>
+      <c r="J58" t="n">
+        <v>-102.0664881662637</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>induction_P_fold</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>BR05</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0.6900480364085393</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.02354891371535377</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.002084250644104035</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.04565359398890776</v>
+      </c>
+      <c r="G59" t="n">
+        <v>55.93598465298017</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.1004445645283111</v>
+      </c>
+      <c r="I59" t="n">
+        <v>-105.6402637244324</v>
+      </c>
+      <c r="J59" t="n">
+        <v>-93.1059944717513</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>induction_P_fold</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>BR07</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0.1707396630055101</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0.08416859522791051</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.03534892528336719</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.1880130987015724</v>
+      </c>
+      <c r="G60" t="n">
+        <v>48.67700964922973</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.279522348796704</v>
+      </c>
+      <c r="I60" t="n">
+        <v>-66.2471568102776</v>
+      </c>
+      <c r="J60" t="n">
+        <v>-50.69711441822565</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>induction_P_fold</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>BR08</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>-0.08254506559110553</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0.1257882467589217</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.04088295963349029</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.2021953501777187</v>
+      </c>
+      <c r="G61" t="n">
+        <v>84.64490028401899</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.7187631828415498</v>
+      </c>
+      <c r="I61" t="n">
+        <v>-55.92604844069487</v>
+      </c>
+      <c r="J61" t="n">
+        <v>-41.29953854227647</v>
       </c>
     </row>
   </sheetData>

--- a/results/modelling/global/metrics_summary_all_models.xlsx
+++ b/results/modelling/global/metrics_summary_all_models.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,311 +479,280 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>parametric_fold</t>
+          <t>global_qP_global</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6170804183178902</v>
+        <v>0.9278070793434743</v>
       </c>
       <c r="C2" t="n">
-        <v>2.105366262903306</v>
+        <v>0.7865269795985638</v>
       </c>
       <c r="D2" t="n">
-        <v>36.07226047152708</v>
+        <v>6.800806129273362</v>
       </c>
       <c r="E2" t="n">
-        <v>6.006018687244245</v>
+        <v>2.607835525732665</v>
       </c>
       <c r="F2" t="n">
-        <v>570.6301770647091</v>
+        <v>18.97949189201213</v>
       </c>
       <c r="G2" t="n">
-        <v>25.37145820457359</v>
+        <v>4.788222166688311</v>
       </c>
       <c r="H2" t="n">
-        <v>1831.104177633461</v>
+        <v>990.1887414034659</v>
       </c>
       <c r="I2" t="n">
-        <v>1881.775092850317</v>
+        <v>1040.859656620322</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>global_qP_global</t>
+          <t>global_rP_global</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9280406073341938</v>
+        <v>0.9273595109519152</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7726756331322739</v>
+        <v>0.7985978839646266</v>
       </c>
       <c r="D3" t="n">
-        <v>6.778807038833483</v>
+        <v>6.842968516290033</v>
       </c>
       <c r="E3" t="n">
-        <v>2.603614226192791</v>
+        <v>2.615906824848705</v>
       </c>
       <c r="F3" t="n">
-        <v>16.98606219421146</v>
+        <v>20.31140201703422</v>
       </c>
       <c r="G3" t="n">
-        <v>4.77275274498318</v>
+        <v>4.817870108117448</v>
       </c>
       <c r="H3" t="n">
-        <v>988.5557712821609</v>
+        <v>993.3037020724471</v>
       </c>
       <c r="I3" t="n">
-        <v>1039.226686499017</v>
+        <v>1043.974617289304</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>global_rP_global</t>
+          <t>global_P_fold</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9279658290751694</v>
+        <v>0.9268513686762052</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7776058356817663</v>
+        <v>0.8568308561595733</v>
       </c>
       <c r="D4" t="n">
-        <v>6.785851392181209</v>
+        <v>6.890837158696571</v>
       </c>
       <c r="E4" t="n">
-        <v>2.604966677748721</v>
+        <v>2.625040410869244</v>
       </c>
       <c r="F4" t="n">
-        <v>17.58473193292106</v>
+        <v>44.84243941022778</v>
       </c>
       <c r="G4" t="n">
-        <v>4.777706225804295</v>
+        <v>4.851530600484738</v>
       </c>
       <c r="H4" t="n">
-        <v>989.0792425401324</v>
+        <v>996.8170608662817</v>
       </c>
       <c r="I4" t="n">
-        <v>1039.750157756989</v>
+        <v>1047.487976083138</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>global_P_fold</t>
+          <t>global_ind_qP_global</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.92796306777117</v>
+        <v>0.9275969530617771</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7874850581396673</v>
+        <v>0.7998485741790295</v>
       </c>
       <c r="D5" t="n">
-        <v>6.786111515930099</v>
+        <v>6.820600703194065</v>
       </c>
       <c r="E5" t="n">
-        <v>2.605016605691814</v>
+        <v>2.61162797947833</v>
       </c>
       <c r="F5" t="n">
-        <v>23.12457196682151</v>
+        <v>23.5490294265498</v>
       </c>
       <c r="G5" t="n">
-        <v>4.777889140819718</v>
+        <v>4.802141406317312</v>
       </c>
       <c r="H5" t="n">
-        <v>989.0985621286612</v>
+        <v>991.6535640024002</v>
       </c>
       <c r="I5" t="n">
-        <v>1039.769477345518</v>
+        <v>1042.324479219257</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>global_ind_qP_global</t>
+          <t>global_ind_rP_global</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9280589786605395</v>
+        <v>0.9271541187191777</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7720935013720499</v>
+        <v>0.8070216325199925</v>
       </c>
       <c r="D6" t="n">
-        <v>6.777076400598053</v>
+        <v>6.862317127519538</v>
       </c>
       <c r="E6" t="n">
-        <v>2.603281851931913</v>
+        <v>2.619602475094177</v>
       </c>
       <c r="F6" t="n">
-        <v>18.54315620118627</v>
+        <v>23.03872818939197</v>
       </c>
       <c r="G6" t="n">
-        <v>4.771535786820476</v>
+        <v>4.831475753647923</v>
       </c>
       <c r="H6" t="n">
-        <v>988.4270830001625</v>
+        <v>994.726759831583</v>
       </c>
       <c r="I6" t="n">
-        <v>1039.097998217019</v>
+        <v>1045.397675048439</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>global_ind_rP_global</t>
+          <t>global_ind_P_fold</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9280140732649141</v>
+        <v>0.9275823472565139</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7827351495147533</v>
+        <v>0.8010407473809297</v>
       </c>
       <c r="D7" t="n">
-        <v>6.781306633798614</v>
+        <v>6.82197661719026</v>
       </c>
       <c r="E7" t="n">
-        <v>2.604094206014563</v>
+        <v>2.611891386943619</v>
       </c>
       <c r="F7" t="n">
-        <v>22.24163844758006</v>
+        <v>27.90013119018987</v>
       </c>
       <c r="G7" t="n">
-        <v>4.774510421679556</v>
+        <v>4.803108927856228</v>
       </c>
       <c r="H7" t="n">
-        <v>988.7415803258177</v>
+        <v>991.7552252413507</v>
       </c>
       <c r="I7" t="n">
-        <v>1039.412495542674</v>
+        <v>1042.426140458207</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>global_ind_P_fold</t>
+          <t>induction_qP_global</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9279532716030739</v>
+        <v>0.9276391850624346</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7858158431132962</v>
+        <v>0.8076510890761722</v>
       </c>
       <c r="D8" t="n">
-        <v>6.787034346581978</v>
+        <v>6.816622312427905</v>
       </c>
       <c r="E8" t="n">
-        <v>2.605193725345963</v>
+        <v>2.610866199641013</v>
       </c>
       <c r="F8" t="n">
-        <v>22.34570947039661</v>
+        <v>32.2373765478484</v>
       </c>
       <c r="G8" t="n">
-        <v>4.778538061126462</v>
+        <v>4.799343863180803</v>
       </c>
       <c r="H8" t="n">
-        <v>989.1670954891622</v>
+        <v>991.3594998808808</v>
       </c>
       <c r="I8" t="n">
-        <v>1039.838010706019</v>
+        <v>1042.030415097737</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>induction_qP_global</t>
+          <t>induction_rP_global</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9276391850624346</v>
+        <v>0.9217826965874376</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8076510890761722</v>
+        <v>0.8888780035488097</v>
       </c>
       <c r="D9" t="n">
-        <v>6.816622312427905</v>
+        <v>7.368322428652223</v>
       </c>
       <c r="E9" t="n">
-        <v>2.610866199641013</v>
+        <v>2.714465403841468</v>
       </c>
       <c r="F9" t="n">
-        <v>32.2373765478484</v>
+        <v>87.42617928402771</v>
       </c>
       <c r="G9" t="n">
-        <v>4.799343863180803</v>
+        <v>5.187290891080325</v>
       </c>
       <c r="H9" t="n">
-        <v>991.3594998808808</v>
+        <v>1030.583789569869</v>
       </c>
       <c r="I9" t="n">
-        <v>1042.030415097737</v>
+        <v>1081.254704786726</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>induction_rP_global</t>
+          <t>induction_P_fold</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9280124657775572</v>
+        <v>0.9278427548704825</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7827132519271389</v>
+        <v>0.7950067186902156</v>
       </c>
       <c r="D10" t="n">
-        <v>6.781458064295815</v>
+        <v>6.797445379486039</v>
       </c>
       <c r="E10" t="n">
-        <v>2.60412328131673</v>
+        <v>2.607191089944509</v>
       </c>
       <c r="F10" t="n">
-        <v>22.21314465309812</v>
+        <v>26.84659779362877</v>
       </c>
       <c r="G10" t="n">
-        <v>4.774616905273803</v>
+        <v>4.785858939179082</v>
       </c>
       <c r="H10" t="n">
-        <v>988.7528348115059</v>
+        <v>989.9396185031861</v>
       </c>
       <c r="I10" t="n">
-        <v>1039.423750028362</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>induction_P_fold</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0.9278060386059956</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.7926221705112618</v>
-      </c>
-      <c r="D11" t="n">
-        <v>6.800904170102839</v>
-      </c>
-      <c r="E11" t="n">
-        <v>2.607854323021675</v>
-      </c>
-      <c r="F11" t="n">
-        <v>22.71078141588476</v>
-      </c>
-      <c r="G11" t="n">
-        <v>4.788291107490189</v>
-      </c>
-      <c r="H11" t="n">
-        <v>990.1960070453549</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1040.866922262211</v>
+        <v>1040.610533720042</v>
       </c>
     </row>
   </sheetData>
@@ -797,7 +766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -855,7 +824,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>parametric_fold</t>
+          <t>global_qP_global</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -864,34 +833,34 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-135.6591363296641</v>
+        <v>0.06029824453133603</v>
       </c>
       <c r="D2" t="n">
-        <v>4.648006464514677</v>
+        <v>0.3424523177632405</v>
       </c>
       <c r="E2" t="n">
-        <v>63.63731111478562</v>
+        <v>0.4375857668499621</v>
       </c>
       <c r="F2" t="n">
-        <v>7.977299738306542</v>
+        <v>0.6615026582334814</v>
       </c>
       <c r="G2" t="n">
-        <v>1045.380126509084</v>
+        <v>56.76774316512636</v>
       </c>
       <c r="H2" t="n">
-        <v>171.0997173584983</v>
+        <v>0.5942205634355726</v>
       </c>
       <c r="I2" t="n">
-        <v>94.60439916837404</v>
+        <v>9.949796583983773</v>
       </c>
       <c r="J2" t="n">
-        <v>104.6029592970486</v>
+        <v>19.94835671265837</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>parametric_fold</t>
+          <t>global_qP_global</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -900,34 +869,34 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-67.00241232875298</v>
+        <v>0.1663131994958235</v>
       </c>
       <c r="D3" t="n">
-        <v>3.022412975155626</v>
+        <v>0.2694908776195508</v>
       </c>
       <c r="E3" t="n">
-        <v>27.0120111204287</v>
+        <v>0.3311582097603272</v>
       </c>
       <c r="F3" t="n">
-        <v>5.197308064799382</v>
+        <v>0.5754634738715632</v>
       </c>
       <c r="G3" t="n">
-        <v>1101.547105775528</v>
+        <v>67.66581614271067</v>
       </c>
       <c r="H3" t="n">
-        <v>78.63026296585198</v>
+        <v>0.4879167869834821</v>
       </c>
       <c r="I3" t="n">
-        <v>73.44422435095905</v>
+        <v>7.422614359619097</v>
       </c>
       <c r="J3" t="n">
-        <v>81.94082676418556</v>
+        <v>15.91921677284562</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>parametric_fold</t>
+          <t>global_qP_global</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -936,34 +905,34 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-3264.481482321026</v>
+        <v>0.8928058360008262</v>
       </c>
       <c r="D4" t="n">
-        <v>3.457856389600832</v>
+        <v>0.0157592359806302</v>
       </c>
       <c r="E4" t="n">
-        <v>42.86773274424948</v>
+        <v>0.001407195477585038</v>
       </c>
       <c r="F4" t="n">
-        <v>6.547345473109654</v>
+        <v>0.03751260424957241</v>
       </c>
       <c r="G4" t="n">
-        <v>6033.091559173914</v>
+        <v>37.14941441918624</v>
       </c>
       <c r="H4" t="n">
-        <v>2019.315715234565</v>
+        <v>0.03914328603406167</v>
       </c>
       <c r="I4" t="n">
-        <v>102.9205072413069</v>
+        <v>-113.8892881446053</v>
       </c>
       <c r="J4" t="n">
-        <v>115.4547764939879</v>
+        <v>-101.3550188919243</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>parametric_fold</t>
+          <t>global_qP_global</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -972,34 +941,34 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-2881.917784130143</v>
+        <v>0.7886358601439594</v>
       </c>
       <c r="D5" t="n">
-        <v>2.090270522989905</v>
+        <v>0.01799935879539229</v>
       </c>
       <c r="E5" t="n">
-        <v>19.38598219817107</v>
+        <v>0.001421303609536432</v>
       </c>
       <c r="F5" t="n">
-        <v>4.402951532571199</v>
+        <v>0.03770018049739858</v>
       </c>
       <c r="G5" t="n">
-        <v>4089.976162178394</v>
+        <v>34.52071971747821</v>
       </c>
       <c r="H5" t="n">
-        <v>1756.903045555525</v>
+        <v>0.07040415448348772</v>
       </c>
       <c r="I5" t="n">
-        <v>86.25555499353264</v>
+        <v>-113.6797966660296</v>
       </c>
       <c r="J5" t="n">
-        <v>98.78982424621373</v>
+        <v>-101.1455274133485</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>parametric_fold</t>
+          <t>global_qP_global</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1008,34 +977,34 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-8495.226043522336</v>
+        <v>0.9873835904061959</v>
       </c>
       <c r="D6" t="n">
-        <v>10.59477225766001</v>
+        <v>0.01407466158585967</v>
       </c>
       <c r="E6" t="n">
-        <v>362.1690875649164</v>
+        <v>0.0005378003748401889</v>
       </c>
       <c r="F6" t="n">
-        <v>19.03074059423113</v>
+        <v>0.02319052338435226</v>
       </c>
       <c r="G6" t="n">
-        <v>5541.195198481908</v>
+        <v>9.004255511125402</v>
       </c>
       <c r="H6" t="n">
-        <v>5604.784348704286</v>
+        <v>0.01016138314052935</v>
       </c>
       <c r="I6" t="n">
-        <v>183.0870022783026</v>
+        <v>-179.2566241628252</v>
       </c>
       <c r="J6" t="n">
-        <v>198.6370446703545</v>
+        <v>-163.7065817707732</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>parametric_fold</t>
+          <t>global_qP_global</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1044,34 +1013,34 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-2321.117397437931</v>
+        <v>0.980633924617773</v>
       </c>
       <c r="D7" t="n">
-        <v>5.967356041367196</v>
+        <v>0.01830895935918366</v>
       </c>
       <c r="E7" t="n">
-        <v>87.69614757039496</v>
+        <v>0.0007313713796093997</v>
       </c>
       <c r="F7" t="n">
-        <v>9.364622126407181</v>
+        <v>0.02704387878262657</v>
       </c>
       <c r="G7" t="n">
-        <v>3240.0904659053</v>
+        <v>19.8238110473178</v>
       </c>
       <c r="H7" t="n">
-        <v>1516.057045061312</v>
+        <v>0.01232178258039468</v>
       </c>
       <c r="I7" t="n">
-        <v>135.8469492762947</v>
+        <v>-156.5147295995864</v>
       </c>
       <c r="J7" t="n">
-        <v>150.473459174713</v>
+        <v>-141.8882197011681</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>global_qP_global</t>
+          <t>global_rP_global</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1080,34 +1049,34 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9492173748221677</v>
+        <v>-1.261585746349521</v>
       </c>
       <c r="D8" t="n">
-        <v>0.08554450998674656</v>
+        <v>0.5233510371016575</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02364766677488337</v>
+        <v>1.053140240883907</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1537779788359939</v>
+        <v>1.026226213309672</v>
       </c>
       <c r="G8" t="n">
-        <v>18.15790677115524</v>
+        <v>83.63165209237656</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03778815429576805</v>
+        <v>2.843347785047184</v>
       </c>
       <c r="I8" t="n">
-        <v>-39.65634403119135</v>
+        <v>24.88019891066671</v>
       </c>
       <c r="J8" t="n">
-        <v>-29.65778390251675</v>
+        <v>34.8787590393413</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>global_qP_global</t>
+          <t>global_rP_global</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1116,34 +1085,34 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.8404511952855884</v>
+        <v>-1.6434277177681</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1187483404733263</v>
+        <v>0.470641754640754</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0633761941614906</v>
+        <v>1.050025969125951</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2517462892705483</v>
+        <v>1.024707748153566</v>
       </c>
       <c r="G9" t="n">
-        <v>32.68656403648551</v>
+        <v>111.135769677212</v>
       </c>
       <c r="H9" t="n">
-        <v>0.09822797732736691</v>
+        <v>3.068092987437192</v>
       </c>
       <c r="I9" t="n">
-        <v>-17.38000461695177</v>
+        <v>24.73222344546742</v>
       </c>
       <c r="J9" t="n">
-        <v>-8.883402203725254</v>
+        <v>33.22882585869394</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>global_qP_global</t>
+          <t>global_rP_global</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1152,34 +1121,34 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.9154276105767704</v>
+        <v>0.9000093055819891</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01755397322903035</v>
+        <v>0.0145394764189158</v>
       </c>
       <c r="E10" t="n">
-        <v>0.001110227268770403</v>
+        <v>0.001312631655830599</v>
       </c>
       <c r="F10" t="n">
-        <v>0.03332007306070026</v>
+        <v>0.03623025884299751</v>
       </c>
       <c r="G10" t="n">
-        <v>33.05813342771476</v>
+        <v>35.36543358208901</v>
       </c>
       <c r="H10" t="n">
-        <v>0.03214887591510818</v>
+        <v>0.03691605048448469</v>
       </c>
       <c r="I10" t="n">
-        <v>-118.8670012974881</v>
+        <v>-115.3501464458221</v>
       </c>
       <c r="J10" t="n">
-        <v>-106.332732044807</v>
+        <v>-102.815877193141</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>global_qP_global</t>
+          <t>global_rP_global</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1188,34 +1157,34 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.9821615565055554</v>
+        <v>0.8027802984604211</v>
       </c>
       <c r="D11" t="n">
-        <v>0.005758768742016479</v>
+        <v>0.01753189056596074</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0001199533853965686</v>
+        <v>0.001326190307688045</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01095232328762115</v>
+        <v>0.03641689590956435</v>
       </c>
       <c r="G11" t="n">
-        <v>14.011728759742</v>
+        <v>34.05607068857816</v>
       </c>
       <c r="H11" t="n">
-        <v>0.01143550041811099</v>
+        <v>0.06609424367725532</v>
       </c>
       <c r="I11" t="n">
-        <v>-165.5965542592595</v>
+        <v>-115.134342425185</v>
       </c>
       <c r="J11" t="n">
-        <v>-153.0622850065784</v>
+        <v>-102.600073172504</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>global_qP_global</t>
+          <t>global_rP_global</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1224,34 +1193,34 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.9816066125563733</v>
+        <v>0.9813474982436131</v>
       </c>
       <c r="D12" t="n">
-        <v>0.01519985788593048</v>
+        <v>0.01524656613677514</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0007840559224251261</v>
+        <v>0.000795101202264275</v>
       </c>
       <c r="F12" t="n">
-        <v>0.02800099859692733</v>
+        <v>0.02819753893984854</v>
       </c>
       <c r="G12" t="n">
-        <v>10.68335084178645</v>
+        <v>9.690688327359176</v>
       </c>
       <c r="H12" t="n">
-        <v>0.01206685537878561</v>
+        <v>0.01215232136850106</v>
       </c>
       <c r="I12" t="n">
-        <v>-169.0778156844131</v>
+        <v>-168.700111130084</v>
       </c>
       <c r="J12" t="n">
-        <v>-153.5277732923611</v>
+        <v>-153.150068738032</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>global_qP_global</t>
+          <t>global_rP_global</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1260,34 +1229,34 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.9879926389243883</v>
+        <v>0.9812305824961248</v>
       </c>
       <c r="D13" t="n">
-        <v>0.01176795089016557</v>
+        <v>0.01810835044846661</v>
       </c>
       <c r="E13" t="n">
-        <v>0.000453465147791266</v>
+        <v>0.0007088382392062897</v>
       </c>
       <c r="F13" t="n">
-        <v>0.02129472112499401</v>
+        <v>0.02662401621105068</v>
       </c>
       <c r="G13" t="n">
-        <v>16.45291755149852</v>
+        <v>19.18166625740643</v>
       </c>
       <c r="H13" t="n">
-        <v>0.009919633926137407</v>
+        <v>0.01212701201860696</v>
       </c>
       <c r="I13" t="n">
-        <v>-168.4648035745064</v>
+        <v>-157.2970802727451</v>
       </c>
       <c r="J13" t="n">
-        <v>-153.838293676088</v>
+        <v>-142.6705703743267</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>global_rP_global</t>
+          <t>global_P_fold</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1296,34 +1265,34 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.8485279139307744</v>
+        <v>0.03747519473844529</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1319014827234317</v>
+        <v>0.3538077184276334</v>
       </c>
       <c r="E14" t="n">
-        <v>0.07053517624419914</v>
+        <v>0.448213651375405</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2655845933863618</v>
+        <v>0.6694876036009965</v>
       </c>
       <c r="G14" t="n">
-        <v>21.24872180965945</v>
+        <v>90.10380100466767</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1008162491917071</v>
+        <v>0.6085069975412499</v>
       </c>
       <c r="I14" t="n">
-        <v>-21.0779435762864</v>
+        <v>10.35775058243996</v>
       </c>
       <c r="J14" t="n">
-        <v>-11.0793834476118</v>
+        <v>20.35631071111456</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>global_rP_global</t>
+          <t>global_P_fold</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1332,34 +1301,34 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.3833119605901091</v>
+        <v>-0.01669120136519964</v>
       </c>
       <c r="D15" t="n">
-        <v>0.219859429584279</v>
+        <v>0.3159362214509615</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2449616654456825</v>
+        <v>0.4038514678648665</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4949360215681241</v>
+        <v>0.6354930903360527</v>
       </c>
       <c r="G15" t="n">
-        <v>50.18302484093834</v>
+        <v>108.9769296159912</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3624795776349451</v>
+        <v>1.187406775829933</v>
       </c>
       <c r="I15" t="n">
-        <v>2.900196776274303</v>
+        <v>10.39937816366924</v>
       </c>
       <c r="J15" t="n">
-        <v>11.39679918950082</v>
+        <v>18.89598057689576</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>global_rP_global</t>
+          <t>global_P_fold</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1368,34 +1337,34 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.8177632614894389</v>
+        <v>-51.81991836155307</v>
       </c>
       <c r="D16" t="n">
-        <v>0.02596456897221756</v>
+        <v>0.501974081930127</v>
       </c>
       <c r="E16" t="n">
-        <v>0.002392319737517474</v>
+        <v>0.6933954934837798</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0489113456931771</v>
+        <v>0.8327037249128767</v>
       </c>
       <c r="G16" t="n">
-        <v>49.4690888819636</v>
+        <v>355.1265392128344</v>
       </c>
       <c r="H16" t="n">
-        <v>0.06234564536943057</v>
+        <v>32.67470470780914</v>
       </c>
       <c r="I16" t="n">
-        <v>-102.7453274282162</v>
+        <v>16.31075035688109</v>
       </c>
       <c r="J16" t="n">
-        <v>-90.21105817553516</v>
+        <v>28.84501960956216</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>global_rP_global</t>
+          <t>global_P_fold</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1404,34 +1373,34 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.988308752471203</v>
+        <v>-105.3629086811794</v>
       </c>
       <c r="D17" t="n">
-        <v>0.004681203230994409</v>
+        <v>0.516647414593433</v>
       </c>
       <c r="E17" t="n">
-        <v>7.861698925835162e-05</v>
+        <v>0.7152300580993459</v>
       </c>
       <c r="F17" t="n">
-        <v>0.008866622201173997</v>
+        <v>0.8457127515293511</v>
       </c>
       <c r="G17" t="n">
-        <v>11.60240256008975</v>
+        <v>497.9877166624406</v>
       </c>
       <c r="H17" t="n">
-        <v>0.009562406151119954</v>
+        <v>64.83106729004673</v>
       </c>
       <c r="I17" t="n">
-        <v>-174.469377404775</v>
+        <v>16.96182840229513</v>
       </c>
       <c r="J17" t="n">
-        <v>-161.9351081520939</v>
+        <v>29.4960976549762</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>global_rP_global</t>
+          <t>global_P_fold</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1440,34 +1409,34 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.9777447102066457</v>
+        <v>-8.646945490880022</v>
       </c>
       <c r="D18" t="n">
-        <v>0.01659403622860814</v>
+        <v>0.3276264082678364</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0009486774429803627</v>
+        <v>0.4112208677503646</v>
       </c>
       <c r="F18" t="n">
-        <v>0.03080060783459253</v>
+        <v>0.6412650526501227</v>
       </c>
       <c r="G18" t="n">
-        <v>10.94804636657624</v>
+        <v>179.3012400629269</v>
       </c>
       <c r="H18" t="n">
-        <v>0.01334066114809256</v>
+        <v>6.375876509378524</v>
       </c>
       <c r="I18" t="n">
-        <v>-163.9319261326304</v>
+        <v>0.00712992186532091</v>
       </c>
       <c r="J18" t="n">
-        <v>-148.3818837405785</v>
+        <v>15.55717231391727</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>global_rP_global</t>
+          <t>global_P_fold</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1476,34 +1445,34 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.9890693161137679</v>
+        <v>-2.720496552229416</v>
       </c>
       <c r="D19" t="n">
-        <v>0.01130598102735859</v>
+        <v>0.2341255080519791</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0004128037920003453</v>
+        <v>0.1405067698297444</v>
       </c>
       <c r="F19" t="n">
-        <v>0.02031757347717353</v>
+        <v>0.3748423266251351</v>
       </c>
       <c r="G19" t="n">
-        <v>15.78022444016893</v>
+        <v>131.0639621346041</v>
       </c>
       <c r="H19" t="n">
-        <v>0.009568167820269868</v>
+        <v>2.441007409099292</v>
       </c>
       <c r="I19" t="n">
-        <v>-170.8134539447941</v>
+        <v>-25.06249018818858</v>
       </c>
       <c r="J19" t="n">
-        <v>-156.1869440463757</v>
+        <v>-10.43598028977018</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>global_P_fold</t>
+          <t>global_ind_qP_global</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1512,34 +1481,34 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.6073303751521468</v>
+        <v>0.1137077420831563</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2283008841795378</v>
+        <v>0.3381689572325551</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1828523123509953</v>
+        <v>0.412714858812094</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4276123388666367</v>
+        <v>0.6424288745161553</v>
       </c>
       <c r="G20" t="n">
-        <v>54.40532814377115</v>
+        <v>61.7322829797148</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2517975061000526</v>
+        <v>0.5607880785435189</v>
       </c>
       <c r="I20" t="n">
-        <v>-4.884300301154614</v>
+        <v>8.955028237586273</v>
       </c>
       <c r="J20" t="n">
-        <v>5.114259827519984</v>
+        <v>18.95358836626087</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>global_P_fold</t>
+          <t>global_ind_qP_global</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1548,34 +1517,34 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.9063456772150384</v>
+        <v>-1.264948344831601</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0897593192099128</v>
+        <v>0.439096317775367</v>
       </c>
       <c r="E21" t="n">
-        <v>0.03720149803382704</v>
+        <v>0.8996858755835511</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1928768986525526</v>
+        <v>0.9485177254978164</v>
       </c>
       <c r="G21" t="n">
-        <v>26.18325774759989</v>
+        <v>107.0338084603909</v>
       </c>
       <c r="H21" t="n">
-        <v>0.06013734545916739</v>
+        <v>2.630529232715932</v>
       </c>
       <c r="I21" t="n">
-        <v>-25.3710937318096</v>
+        <v>22.41435594432961</v>
       </c>
       <c r="J21" t="n">
-        <v>-16.87449131858308</v>
+        <v>30.91095835755613</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>global_P_fold</t>
+          <t>global_ind_qP_global</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1584,34 +1553,34 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.9641675638716671</v>
+        <v>-3.817280438826588</v>
       </c>
       <c r="D22" t="n">
-        <v>0.01172495433638124</v>
+        <v>0.09341914364653818</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0004703916723585195</v>
+        <v>0.0632390327502147</v>
       </c>
       <c r="F22" t="n">
-        <v>0.02168851475685966</v>
+        <v>0.2514737217886089</v>
       </c>
       <c r="G22" t="n">
-        <v>21.98109466612958</v>
+        <v>112.0809736995915</v>
       </c>
       <c r="H22" t="n">
-        <v>0.01707900500915083</v>
+        <v>2.990902909146254</v>
       </c>
       <c r="I22" t="n">
-        <v>-136.9008421619768</v>
+        <v>-33.97750479491722</v>
       </c>
       <c r="J22" t="n">
-        <v>-124.3665729092957</v>
+        <v>-21.44323554223615</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>global_P_fold</t>
+          <t>global_ind_qP_global</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1620,34 +1589,34 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.7112695284327581</v>
+        <v>0.4988981055930591</v>
       </c>
       <c r="D23" t="n">
-        <v>0.02647791321291858</v>
+        <v>0.02456995765585735</v>
       </c>
       <c r="E23" t="n">
-        <v>0.001941548181735942</v>
+        <v>0.00336962519636121</v>
       </c>
       <c r="F23" t="n">
-        <v>0.04406300241399742</v>
+        <v>0.05804847281678658</v>
       </c>
       <c r="G23" t="n">
-        <v>64.14814689420729</v>
+        <v>49.54506830130952</v>
       </c>
       <c r="H23" t="n">
-        <v>0.09397822519738773</v>
+        <v>0.1586893059595351</v>
       </c>
       <c r="I23" t="n">
-        <v>-107.1296614391891</v>
+        <v>-95.55202892849967</v>
       </c>
       <c r="J23" t="n">
-        <v>-94.59539218650798</v>
+        <v>-83.01775967581858</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>global_P_fold</t>
+          <t>global_ind_qP_global</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1656,34 +1625,34 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.3463106845898629</v>
+        <v>0.931974266010735</v>
       </c>
       <c r="D24" t="n">
-        <v>0.08940744106400159</v>
+        <v>0.03420504944489605</v>
       </c>
       <c r="E24" t="n">
-        <v>0.02786484984042101</v>
+        <v>0.00289973664584988</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1669276784731071</v>
+        <v>0.05384920283393135</v>
       </c>
       <c r="G24" t="n">
-        <v>53.15665304553558</v>
+        <v>22.57769778950628</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2216121895113358</v>
+        <v>0.02843753584887443</v>
       </c>
       <c r="I24" t="n">
-        <v>-72.67050966357553</v>
+        <v>-133.7646546630098</v>
       </c>
       <c r="J24" t="n">
-        <v>-57.12046727152358</v>
+        <v>-118.2146122709578</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>global_P_fold</t>
+          <t>global_ind_qP_global</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1692,34 +1661,34 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.3402080224833306</v>
+        <v>0.4847327443599516</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1379931415225295</v>
+        <v>0.09552728278820942</v>
       </c>
       <c r="E25" t="n">
-        <v>0.02491743728801341</v>
+        <v>0.01945937502499157</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1578525808721967</v>
+        <v>0.1394968638536063</v>
       </c>
       <c r="G25" t="n">
-        <v>94.49535701683655</v>
+        <v>62.2177435344468</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2213797993566102</v>
+        <v>0.1742017392095087</v>
       </c>
       <c r="I25" t="n">
-        <v>-68.3046856977671</v>
+        <v>-74.48565796547906</v>
       </c>
       <c r="J25" t="n">
-        <v>-53.67817579934869</v>
+        <v>-59.85914806706066</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>global_ind_qP_global</t>
+          <t>global_ind_rP_global</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1728,34 +1697,34 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.9958241535455704</v>
+        <v>-1.399581460400566</v>
       </c>
       <c r="D26" t="n">
-        <v>0.02798856055435583</v>
+        <v>0.5416457247711814</v>
       </c>
       <c r="E26" t="n">
-        <v>0.001944543534557873</v>
+        <v>1.117399948821686</v>
       </c>
       <c r="F26" t="n">
-        <v>0.04409697874637074</v>
+        <v>1.057071401950543</v>
       </c>
       <c r="G26" t="n">
-        <v>14.80477021707731</v>
+        <v>89.28599930727141</v>
       </c>
       <c r="H26" t="n">
-        <v>0.008613934410519388</v>
+        <v>3.0161088045907</v>
       </c>
       <c r="I26" t="n">
-        <v>-82.12637627297875</v>
+        <v>25.88707670810827</v>
       </c>
       <c r="J26" t="n">
-        <v>-72.12781614430415</v>
+        <v>35.88563683678287</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>global_ind_qP_global</t>
+          <t>global_ind_rP_global</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1764,34 +1733,34 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.9850187497845564</v>
+        <v>-3.009513658119724</v>
       </c>
       <c r="D27" t="n">
-        <v>0.04027540788310947</v>
+        <v>0.5866676971590761</v>
       </c>
       <c r="E27" t="n">
-        <v>0.005950872675826841</v>
+        <v>1.592664492504288</v>
       </c>
       <c r="F27" t="n">
-        <v>0.07714189961251175</v>
+        <v>1.262008119032635</v>
       </c>
       <c r="G27" t="n">
-        <v>20.67325629683002</v>
+        <v>143.6650718672136</v>
       </c>
       <c r="H27" t="n">
-        <v>0.01465998593771187</v>
+        <v>4.647438484377838</v>
       </c>
       <c r="I27" t="n">
-        <v>-52.86326102959704</v>
+        <v>30.98112592689516</v>
       </c>
       <c r="J27" t="n">
-        <v>-44.36665861637052</v>
+        <v>39.47772834012167</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>global_ind_qP_global</t>
+          <t>global_ind_rP_global</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1800,34 +1769,34 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.9783962967836752</v>
+        <v>0.9455472972276772</v>
       </c>
       <c r="D28" t="n">
-        <v>0.007866928860550676</v>
+        <v>0.01251523870492765</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0002836034381996378</v>
+        <v>0.0007148299331303663</v>
       </c>
       <c r="F28" t="n">
-        <v>0.01684052962942786</v>
+        <v>0.0267363036549626</v>
       </c>
       <c r="G28" t="n">
-        <v>18.13821325768107</v>
+        <v>26.97849654063086</v>
       </c>
       <c r="H28" t="n">
-        <v>0.01267963337163718</v>
+        <v>0.02283619178488811</v>
       </c>
       <c r="I28" t="n">
-        <v>-147.526606439324</v>
+        <v>-128.1127838858073</v>
       </c>
       <c r="J28" t="n">
-        <v>-134.9923371866429</v>
+        <v>-115.5785146331263</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>global_ind_qP_global</t>
+          <t>global_ind_rP_global</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1836,34 +1805,34 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.9402673302427061</v>
+        <v>0.710784203995128</v>
       </c>
       <c r="D29" t="n">
-        <v>0.01049836218812276</v>
+        <v>0.02192074313926802</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0004016682261764622</v>
+        <v>0.001944811712510225</v>
       </c>
       <c r="F29" t="n">
-        <v>0.02004166226081215</v>
+        <v>0.04410001941621143</v>
       </c>
       <c r="G29" t="n">
-        <v>28.09948012714894</v>
+        <v>45.43644146323128</v>
       </c>
       <c r="H29" t="n">
-        <v>0.02420096868551169</v>
+        <v>0.09412610700021877</v>
       </c>
       <c r="I29" t="n">
-        <v>-140.2175664804815</v>
+        <v>-107.0943923626063</v>
       </c>
       <c r="J29" t="n">
-        <v>-127.6832972278004</v>
+        <v>-94.5601231099252</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>global_ind_qP_global</t>
+          <t>global_ind_rP_global</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1872,34 +1841,34 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.9774666981486664</v>
+        <v>0.9753731689637943</v>
       </c>
       <c r="D30" t="n">
-        <v>0.01965699137212053</v>
+        <v>0.02048844167033197</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0009605282780281379</v>
+        <v>0.001049769259940776</v>
       </c>
       <c r="F30" t="n">
-        <v>0.03099239064719174</v>
+        <v>0.03240014290000549</v>
       </c>
       <c r="G30" t="n">
-        <v>15.87098348203059</v>
+        <v>15.18927050267564</v>
       </c>
       <c r="H30" t="n">
-        <v>0.01343236035001978</v>
+        <v>0.01412288779282024</v>
       </c>
       <c r="I30" t="n">
-        <v>-163.596732651576</v>
+        <v>-161.1979920677775</v>
       </c>
       <c r="J30" t="n">
-        <v>-148.046690259524</v>
+        <v>-145.6479496757255</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>global_ind_qP_global</t>
+          <t>global_ind_rP_global</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1908,34 +1877,34 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.6016416101951607</v>
+        <v>0.4385208405315066</v>
       </c>
       <c r="D31" t="n">
-        <v>0.08559613403744323</v>
+        <v>0.09822766601827851</v>
       </c>
       <c r="E31" t="n">
-        <v>0.01504424202530608</v>
+        <v>0.02120459511684377</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1226549714659218</v>
+        <v>0.1456179766266644</v>
       </c>
       <c r="G31" t="n">
-        <v>57.65079950440185</v>
+        <v>63.21948198834598</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1360384863591661</v>
+        <v>0.1892869644223387</v>
       </c>
       <c r="I31" t="n">
-        <v>-80.91899876685041</v>
+        <v>-72.33843424991781</v>
       </c>
       <c r="J31" t="n">
-        <v>-66.292488868432</v>
+        <v>-57.71192435149941</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>global_ind_rP_global</t>
+          <t>global_ind_P_fold</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1944,34 +1913,34 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.942480770334623</v>
+        <v>0.28905427992869</v>
       </c>
       <c r="D32" t="n">
-        <v>0.09779218834126532</v>
+        <v>0.3438732986019148</v>
       </c>
       <c r="E32" t="n">
-        <v>0.02678466446962219</v>
+        <v>0.3310621974425766</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1636602104044297</v>
+        <v>0.575380046093516</v>
       </c>
       <c r="G32" t="n">
-        <v>27.87667178736398</v>
+        <v>131.8988938081492</v>
       </c>
       <c r="H32" t="n">
-        <v>0.04200503402834865</v>
+        <v>0.4510272542311967</v>
       </c>
       <c r="I32" t="n">
-        <v>-37.53873820099573</v>
+        <v>5.207366769207816</v>
       </c>
       <c r="J32" t="n">
-        <v>-27.54017807232113</v>
+        <v>15.20592689788241</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>global_ind_rP_global</t>
+          <t>global_ind_P_fold</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1980,34 +1949,34 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.9036227460136417</v>
+        <v>-0.310968506839814</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1101547893929558</v>
+        <v>0.3575417747760513</v>
       </c>
       <c r="E33" t="n">
-        <v>0.03828310448532633</v>
+        <v>0.520744701145196</v>
       </c>
       <c r="F33" t="n">
-        <v>0.195660687122698</v>
+        <v>0.7216264276931631</v>
       </c>
       <c r="G33" t="n">
-        <v>43.74061146977564</v>
+        <v>154.0376441141564</v>
       </c>
       <c r="H33" t="n">
-        <v>0.06171134933563593</v>
+        <v>1.527623685707163</v>
       </c>
       <c r="I33" t="n">
-        <v>-24.94119924417111</v>
+        <v>14.21256938516823</v>
       </c>
       <c r="J33" t="n">
-        <v>-16.44459683094459</v>
+        <v>22.70917179839475</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>global_ind_rP_global</t>
+          <t>global_ind_P_fold</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2016,34 +1985,34 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.7549856722491133</v>
+        <v>-32.89908337648875</v>
       </c>
       <c r="D34" t="n">
-        <v>0.02976845441713929</v>
+        <v>0.22071248025575</v>
       </c>
       <c r="E34" t="n">
-        <v>0.003216434935368715</v>
+        <v>0.4450115103471561</v>
       </c>
       <c r="F34" t="n">
-        <v>0.05671362213233003</v>
+        <v>0.6670918305204735</v>
       </c>
       <c r="G34" t="n">
-        <v>55.28776858508739</v>
+        <v>243.2365366145559</v>
       </c>
       <c r="H34" t="n">
-        <v>0.08175580278002413</v>
+        <v>20.97446614037927</v>
       </c>
       <c r="I34" t="n">
-        <v>-96.5291156099611</v>
+        <v>6.997242244763264</v>
       </c>
       <c r="J34" t="n">
-        <v>-83.99484635728001</v>
+        <v>19.53151149744434</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>global_ind_rP_global</t>
+          <t>global_ind_P_fold</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2052,34 +2021,34 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.4517496294332493</v>
+        <v>0.0905084597817456</v>
       </c>
       <c r="D35" t="n">
-        <v>0.03109105393290582</v>
+        <v>0.04122559867976912</v>
       </c>
       <c r="E35" t="n">
-        <v>0.003686671878905005</v>
+        <v>0.006115813258746176</v>
       </c>
       <c r="F35" t="n">
-        <v>0.06071796998339952</v>
+        <v>0.07820366525135619</v>
       </c>
       <c r="G35" t="n">
-        <v>70.48143675492847</v>
+        <v>101.6616171077164</v>
       </c>
       <c r="H35" t="n">
-        <v>0.1730557814852588</v>
+        <v>0.2831285313465987</v>
       </c>
       <c r="I35" t="n">
-        <v>-93.663654312733</v>
+        <v>-83.0344280169066</v>
       </c>
       <c r="J35" t="n">
-        <v>-81.12938506005193</v>
+        <v>-70.50015876422552</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>global_ind_rP_global</t>
+          <t>global_ind_P_fold</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2088,34 +2057,34 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.8061014216803246</v>
+        <v>0.9630114372706771</v>
       </c>
       <c r="D36" t="n">
-        <v>0.05537383712791812</v>
+        <v>0.02331838321916886</v>
       </c>
       <c r="E36" t="n">
-        <v>0.008265325196204184</v>
+        <v>0.001576713466119466</v>
       </c>
       <c r="F36" t="n">
-        <v>0.09091383390994015</v>
+        <v>0.03970785144174217</v>
       </c>
       <c r="G36" t="n">
-        <v>37.48765349370173</v>
+        <v>17.69597515393271</v>
       </c>
       <c r="H36" t="n">
-        <v>0.06995530113324556</v>
+        <v>0.01820026824508051</v>
       </c>
       <c r="I36" t="n">
-        <v>-105.4835274620996</v>
+        <v>-150.2151424425854</v>
       </c>
       <c r="J36" t="n">
-        <v>-89.93348507004768</v>
+        <v>-134.6651000505335</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>global_ind_rP_global</t>
+          <t>global_ind_P_fold</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2124,34 +2093,34 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-0.3483953177459476</v>
+        <v>0.7744110833231334</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1364683285376958</v>
+        <v>0.05545572638747715</v>
       </c>
       <c r="E37" t="n">
-        <v>0.05092295286136107</v>
+        <v>0.008519499896502896</v>
       </c>
       <c r="F37" t="n">
-        <v>0.2256611461048647</v>
+        <v>0.09230113702714011</v>
       </c>
       <c r="G37" t="n">
-        <v>77.80710050469769</v>
+        <v>35.81103891781405</v>
       </c>
       <c r="H37" t="n">
-        <v>0.8923293246534741</v>
+        <v>0.07964032493061203</v>
       </c>
       <c r="I37" t="n">
-        <v>-50.43603791917234</v>
+        <v>-95.13494093643102</v>
       </c>
       <c r="J37" t="n">
-        <v>-35.80952802075393</v>
+        <v>-80.50843103801262</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>global_ind_P_fold</t>
+          <t>induction_qP_global</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2160,34 +2129,34 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.7143759036629604</v>
+        <v>0.4233650413754192</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1541016707379723</v>
+        <v>0.3127000696595981</v>
       </c>
       <c r="E38" t="n">
-        <v>0.1330050077049567</v>
+        <v>0.2685184411902992</v>
       </c>
       <c r="F38" t="n">
-        <v>0.3646985161814573</v>
+        <v>0.5181876505574976</v>
       </c>
       <c r="G38" t="n">
-        <v>29.38175095621351</v>
+        <v>82.83084249974198</v>
       </c>
       <c r="H38" t="n">
-        <v>0.1847907342945815</v>
+        <v>0.3669533964205837</v>
       </c>
       <c r="I38" t="n">
-        <v>-10.29526449238794</v>
+        <v>1.647793352981392</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.2967043637133386</v>
+        <v>11.64635348165599</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>global_ind_P_fold</t>
+          <t>induction_qP_global</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2196,34 +2165,34 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.9357590505026809</v>
+        <v>-0.6268942863405074</v>
       </c>
       <c r="D39" t="n">
-        <v>0.07464108127115485</v>
+        <v>0.4324432358406863</v>
       </c>
       <c r="E39" t="n">
-        <v>0.02551787771615221</v>
+        <v>0.6462371708512237</v>
       </c>
       <c r="F39" t="n">
-        <v>0.1597431617195309</v>
+        <v>0.8038887801501049</v>
       </c>
       <c r="G39" t="n">
-        <v>25.34967087143018</v>
+        <v>139.0873590754149</v>
       </c>
       <c r="H39" t="n">
-        <v>0.04313479925050227</v>
+        <v>1.892868610996018</v>
       </c>
       <c r="I39" t="n">
-        <v>-31.0256397833467</v>
+        <v>17.45116942443844</v>
       </c>
       <c r="J39" t="n">
-        <v>-22.52903737012019</v>
+        <v>25.94777183766496</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>global_ind_P_fold</t>
+          <t>induction_qP_global</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2232,34 +2201,34 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.9489093458003982</v>
+        <v>-17.75539577796259</v>
       </c>
       <c r="D40" t="n">
-        <v>0.01020567355451904</v>
+        <v>0.2651263845329371</v>
       </c>
       <c r="E40" t="n">
-        <v>0.0006706945122226501</v>
+        <v>0.2462121736335374</v>
       </c>
       <c r="F40" t="n">
-        <v>0.02589777041026216</v>
+        <v>0.4961977162719891</v>
       </c>
       <c r="G40" t="n">
-        <v>16.0075324138305</v>
+        <v>493.4171585079131</v>
       </c>
       <c r="H40" t="n">
-        <v>0.02179668241843639</v>
+        <v>11.60993450986451</v>
       </c>
       <c r="I40" t="n">
-        <v>-129.4511327381758</v>
+        <v>-5.432794027121176</v>
       </c>
       <c r="J40" t="n">
-        <v>-116.9168634854947</v>
+        <v>7.101475225559902</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>global_ind_P_fold</t>
+          <t>induction_qP_global</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2268,34 +2237,34 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-0.1061125155919211</v>
+        <v>0.8714327281533696</v>
       </c>
       <c r="D41" t="n">
-        <v>0.04125598283481639</v>
+        <v>0.01486866392062623</v>
       </c>
       <c r="E41" t="n">
-        <v>0.007437977473543939</v>
+        <v>0.0008645417698022307</v>
       </c>
       <c r="F41" t="n">
-        <v>0.08624370976218462</v>
+        <v>0.02940309116066252</v>
       </c>
       <c r="G41" t="n">
-        <v>84.34546561333883</v>
+        <v>34.99271128998283</v>
       </c>
       <c r="H41" t="n">
-        <v>0.6860806778181142</v>
+        <v>0.04517536079285069</v>
       </c>
       <c r="I41" t="n">
-        <v>-78.92428255299635</v>
+        <v>-124.1195296831047</v>
       </c>
       <c r="J41" t="n">
-        <v>-66.39001330031527</v>
+        <v>-111.5852604304236</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>global_ind_P_fold</t>
+          <t>induction_qP_global</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2304,34 +2273,34 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.05529769846160315</v>
+        <v>0.3232122409296073</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0912661401784936</v>
+        <v>0.1021986447853731</v>
       </c>
       <c r="E42" t="n">
-        <v>0.04026987615630736</v>
+        <v>0.02884946844893631</v>
       </c>
       <c r="F42" t="n">
-        <v>0.2006735561958958</v>
+        <v>0.1698513127677743</v>
       </c>
       <c r="G42" t="n">
-        <v>50.47121902571124</v>
+        <v>65.14800806952728</v>
       </c>
       <c r="H42" t="n">
-        <v>0.3175996037709343</v>
+        <v>0.2292309556353732</v>
       </c>
       <c r="I42" t="n">
-        <v>-62.72809264534753</v>
+        <v>-71.73292019280652</v>
       </c>
       <c r="J42" t="n">
-        <v>-47.17805025329558</v>
+        <v>-56.18287780075457</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>global_ind_P_fold</t>
+          <t>induction_qP_global</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2340,34 +2309,34 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-0.754119254784154</v>
+        <v>0.7415923234793511</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1507233968251267</v>
+        <v>0.06461859689114323</v>
       </c>
       <c r="E43" t="n">
-        <v>0.06624535916803671</v>
+        <v>0.009758919923032634</v>
       </c>
       <c r="F43" t="n">
-        <v>0.25738173821784</v>
+        <v>0.09878724575081864</v>
       </c>
       <c r="G43" t="n">
-        <v>86.24485387074829</v>
+        <v>55.04843430658151</v>
       </c>
       <c r="H43" t="n">
-        <v>1.157215055705744</v>
+        <v>0.09035354690231753</v>
       </c>
       <c r="I43" t="n">
-        <v>-43.85974667158068</v>
+        <v>-91.73933870761279</v>
       </c>
       <c r="J43" t="n">
-        <v>-29.23323677316228</v>
+        <v>-77.11282880919438</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>induction_qP_global</t>
+          <t>induction_rP_global</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2376,34 +2345,34 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.4233650413754192</v>
+        <v>-0.2129063581347828</v>
       </c>
       <c r="D44" t="n">
-        <v>0.3127000696595981</v>
+        <v>0.4580469069190481</v>
       </c>
       <c r="E44" t="n">
-        <v>0.2685184411902992</v>
+        <v>0.5648074569967135</v>
       </c>
       <c r="F44" t="n">
-        <v>0.5181876505574976</v>
+        <v>0.7515367303044566</v>
       </c>
       <c r="G44" t="n">
-        <v>82.83084249974198</v>
+        <v>114.5212251150281</v>
       </c>
       <c r="H44" t="n">
-        <v>0.3669533964205837</v>
+        <v>1.530474254676269</v>
       </c>
       <c r="I44" t="n">
-        <v>1.647793352981392</v>
+        <v>14.28840337012923</v>
       </c>
       <c r="J44" t="n">
-        <v>11.64635348165599</v>
+        <v>24.28696349880383</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>induction_qP_global</t>
+          <t>induction_rP_global</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2412,34 +2381,34 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-0.6268942863405074</v>
+        <v>-3.256057844739419</v>
       </c>
       <c r="D45" t="n">
-        <v>0.4324432358406863</v>
+        <v>0.7056260605136777</v>
       </c>
       <c r="E45" t="n">
-        <v>0.6462371708512237</v>
+        <v>1.690597111106885</v>
       </c>
       <c r="F45" t="n">
-        <v>0.8038887801501049</v>
+        <v>1.300229637835904</v>
       </c>
       <c r="G45" t="n">
-        <v>139.0873590754149</v>
+        <v>220.5657154205258</v>
       </c>
       <c r="H45" t="n">
-        <v>1.892868610996018</v>
+        <v>4.93247066239329</v>
       </c>
       <c r="I45" t="n">
-        <v>17.45116942443844</v>
+        <v>31.8762268007054</v>
       </c>
       <c r="J45" t="n">
-        <v>25.94777183766496</v>
+        <v>40.37282921393192</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>induction_qP_global</t>
+          <t>induction_rP_global</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2448,34 +2417,34 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-17.75539577796259</v>
+        <v>-951.1363667347894</v>
       </c>
       <c r="D46" t="n">
-        <v>0.2651263845329371</v>
+        <v>1.889748525057547</v>
       </c>
       <c r="E46" t="n">
-        <v>0.2462121736335374</v>
+        <v>12.49920648034319</v>
       </c>
       <c r="F46" t="n">
-        <v>0.4961977162719891</v>
+        <v>3.535421683525629</v>
       </c>
       <c r="G46" t="n">
-        <v>493.4171585079131</v>
+        <v>3541.430862015478</v>
       </c>
       <c r="H46" t="n">
-        <v>11.60993450986451</v>
+        <v>588.7927091133541</v>
       </c>
       <c r="I46" t="n">
-        <v>-5.432794027121176</v>
+        <v>77.03896837513409</v>
       </c>
       <c r="J46" t="n">
-        <v>7.101475225559902</v>
+        <v>89.57323762781516</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>induction_qP_global</t>
+          <t>induction_rP_global</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2484,34 +2453,34 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.8714327281533696</v>
+        <v>0.8152370113312783</v>
       </c>
       <c r="D47" t="n">
-        <v>0.01486866392062623</v>
+        <v>0.0180160511765564</v>
       </c>
       <c r="E47" t="n">
-        <v>0.0008645417698022307</v>
+        <v>0.001242425999426638</v>
       </c>
       <c r="F47" t="n">
-        <v>0.02940309116066252</v>
+        <v>0.03524806376847724</v>
       </c>
       <c r="G47" t="n">
-        <v>34.99271128998283</v>
+        <v>40.58914791880778</v>
       </c>
       <c r="H47" t="n">
-        <v>0.04517536079285069</v>
+        <v>0.06229859480021515</v>
       </c>
       <c r="I47" t="n">
-        <v>-124.1195296831047</v>
+        <v>-116.5044765510256</v>
       </c>
       <c r="J47" t="n">
-        <v>-111.5852604304236</v>
+        <v>-103.9702072983446</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>induction_qP_global</t>
+          <t>induction_rP_global</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2520,34 +2489,34 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.3232122409296073</v>
+        <v>0.3554148587405159</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1021986447853731</v>
+        <v>0.1036522115411825</v>
       </c>
       <c r="E48" t="n">
-        <v>0.02884946844893631</v>
+        <v>0.02747676571597755</v>
       </c>
       <c r="F48" t="n">
-        <v>0.1698513127677743</v>
+        <v>0.1657611707124969</v>
       </c>
       <c r="G48" t="n">
-        <v>65.14800806952728</v>
+        <v>66.6646523962947</v>
       </c>
       <c r="H48" t="n">
-        <v>0.2292309556353732</v>
+        <v>0.2186092783790295</v>
       </c>
       <c r="I48" t="n">
-        <v>-71.73292019280652</v>
+        <v>-73.04919189095521</v>
       </c>
       <c r="J48" t="n">
-        <v>-56.18287780075457</v>
+        <v>-57.49914949890326</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>induction_qP_global</t>
+          <t>induction_rP_global</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2556,34 +2525,34 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.7415923234793511</v>
+        <v>0.6666104453755446</v>
       </c>
       <c r="D49" t="n">
-        <v>0.06461859689114323</v>
+        <v>0.07051139344685514</v>
       </c>
       <c r="E49" t="n">
-        <v>0.009758919923032634</v>
+        <v>0.01259065524121762</v>
       </c>
       <c r="F49" t="n">
-        <v>0.09878724575081864</v>
+        <v>0.1122080890186515</v>
       </c>
       <c r="G49" t="n">
-        <v>55.04843430658151</v>
+        <v>59.81587240746438</v>
       </c>
       <c r="H49" t="n">
-        <v>0.09035354690231753</v>
+        <v>0.114830325056189</v>
       </c>
       <c r="I49" t="n">
-        <v>-91.73933870761279</v>
+        <v>-85.37000969259236</v>
       </c>
       <c r="J49" t="n">
-        <v>-77.11282880919438</v>
+        <v>-70.74349979417396</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>induction_rP_global</t>
+          <t>induction_P_fold</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2592,34 +2561,34 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.9414505858506642</v>
+        <v>0.3727225967834948</v>
       </c>
       <c r="D50" t="n">
-        <v>0.09843301642931242</v>
+        <v>0.2622257011901458</v>
       </c>
       <c r="E50" t="n">
-        <v>0.0272643848327976</v>
+        <v>0.2921008308399405</v>
       </c>
       <c r="F50" t="n">
-        <v>0.1651193048459131</v>
+        <v>0.5404635333118605</v>
       </c>
       <c r="G50" t="n">
-        <v>27.62974601975025</v>
+        <v>42.01778878792659</v>
       </c>
       <c r="H50" t="n">
-        <v>0.04264989362775905</v>
+        <v>0.3986538025529099</v>
       </c>
       <c r="I50" t="n">
-        <v>-37.23695822749603</v>
+        <v>3.078844171186496</v>
       </c>
       <c r="J50" t="n">
-        <v>-27.23839809882143</v>
+        <v>13.07740429986109</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>induction_rP_global</t>
+          <t>induction_P_fold</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2628,34 +2597,34 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.9090737847592535</v>
+        <v>0.601776087518032</v>
       </c>
       <c r="D51" t="n">
-        <v>0.1060456855431119</v>
+        <v>0.1557010632353629</v>
       </c>
       <c r="E51" t="n">
-        <v>0.03611783542836233</v>
+        <v>0.1581830465128266</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1900469295420537</v>
+        <v>0.3977223233775375</v>
       </c>
       <c r="G51" t="n">
-        <v>42.80516230744533</v>
+        <v>31.64442937755998</v>
       </c>
       <c r="H51" t="n">
-        <v>0.05856034937207758</v>
+        <v>0.236195306303569</v>
       </c>
       <c r="I51" t="n">
-        <v>-25.81452719192332</v>
+        <v>-3.660035914366656</v>
       </c>
       <c r="J51" t="n">
-        <v>-17.3179247786968</v>
+        <v>4.836566498859863</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>induction_rP_global</t>
+          <t>induction_P_fold</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2664,34 +2633,34 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.7869683992505639</v>
+        <v>-2.292501058686348</v>
       </c>
       <c r="D52" t="n">
-        <v>0.0274949305475261</v>
+        <v>0.0971029138896892</v>
       </c>
       <c r="E52" t="n">
-        <v>0.002796580466447951</v>
+        <v>0.04322243326383968</v>
       </c>
       <c r="F52" t="n">
-        <v>0.05288270479512135</v>
+        <v>0.2079000559495829</v>
       </c>
       <c r="G52" t="n">
-        <v>52.26240803301273</v>
+        <v>143.0485653997427</v>
       </c>
       <c r="H52" t="n">
-        <v>0.0718670865513444</v>
+        <v>2.048012041781185</v>
       </c>
       <c r="I52" t="n">
-        <v>-99.46651527277176</v>
+        <v>-41.96930823001863</v>
       </c>
       <c r="J52" t="n">
-        <v>-86.93224602009067</v>
+        <v>-29.43503897733755</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>induction_rP_global</t>
+          <t>induction_P_fold</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2700,34 +2669,34 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.5047725476255526</v>
+        <v>-10.4235652104228</v>
       </c>
       <c r="D53" t="n">
-        <v>0.02945417730549118</v>
+        <v>0.1264924492953734</v>
       </c>
       <c r="E53" t="n">
-        <v>0.003330122915271892</v>
+        <v>0.07681697793394504</v>
       </c>
       <c r="F53" t="n">
-        <v>0.0577072171853044</v>
+        <v>0.2771587594393239</v>
       </c>
       <c r="G53" t="n">
-        <v>67.50433929176376</v>
+        <v>241.0218086385581</v>
       </c>
       <c r="H53" t="n">
-        <v>0.1568993217530246</v>
+        <v>6.973682895361207</v>
       </c>
       <c r="I53" t="n">
-        <v>-95.79966734773667</v>
+        <v>-29.8929215246508</v>
       </c>
       <c r="J53" t="n">
-        <v>-83.26539809505559</v>
+        <v>-17.35865227196972</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>induction_rP_global</t>
+          <t>induction_P_fold</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2736,34 +2705,34 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.8244859104919592</v>
+        <v>0.6319812958585576</v>
       </c>
       <c r="D54" t="n">
-        <v>0.05323417232392352</v>
+        <v>0.06340137598747402</v>
       </c>
       <c r="E54" t="n">
-        <v>0.007481648596246778</v>
+        <v>0.01568755322692337</v>
       </c>
       <c r="F54" t="n">
-        <v>0.0864965236078698</v>
+        <v>0.1252499629817245</v>
       </c>
       <c r="G54" t="n">
-        <v>36.3684899105393</v>
+        <v>40.12670930054983</v>
       </c>
       <c r="H54" t="n">
-        <v>0.06389138086978499</v>
+        <v>0.1273868985012791</v>
       </c>
       <c r="I54" t="n">
-        <v>-108.1731569892412</v>
+        <v>-88.18196706690422</v>
       </c>
       <c r="J54" t="n">
-        <v>-92.62311459718927</v>
+        <v>-72.63192467485227</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>induction_rP_global</t>
+          <t>induction_P_fold</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2772,244 +2741,28 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>-0.4946752146282869</v>
+        <v>0.447258575977301</v>
       </c>
       <c r="D55" t="n">
-        <v>0.1436521470797448</v>
+        <v>0.09935275018770522</v>
       </c>
       <c r="E55" t="n">
-        <v>0.05644730035461423</v>
+        <v>0.02087460932976388</v>
       </c>
       <c r="F55" t="n">
-        <v>0.2375864060812702</v>
+        <v>0.1444804807915723</v>
       </c>
       <c r="G55" t="n">
-        <v>81.25457401305202</v>
+        <v>75.89669421584698</v>
       </c>
       <c r="H55" t="n">
-        <v>0.9878313492734322</v>
+        <v>0.1864346537376445</v>
       </c>
       <c r="I55" t="n">
-        <v>-47.86119532965336</v>
+        <v>-72.73054307905477</v>
       </c>
       <c r="J55" t="n">
-        <v>-33.23468543123495</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>induction_P_fold</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>BR02</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>0.07857686751760085</v>
-      </c>
-      <c r="D56" t="n">
-        <v>0.3333337353130066</v>
-      </c>
-      <c r="E56" t="n">
-        <v>0.4290740606518431</v>
-      </c>
-      <c r="F56" t="n">
-        <v>0.6550374498086678</v>
-      </c>
-      <c r="G56" t="n">
-        <v>55.21890071551628</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0.5827787822010099</v>
-      </c>
-      <c r="I56" t="n">
-        <v>9.615862430168713</v>
-      </c>
-      <c r="J56" t="n">
-        <v>19.61442255884331</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>induction_P_fold</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>BR03</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>0.462120720638594</v>
-      </c>
-      <c r="D57" t="n">
-        <v>0.1677181877507518</v>
-      </c>
-      <c r="E57" t="n">
-        <v>0.2136571421219302</v>
-      </c>
-      <c r="F57" t="n">
-        <v>0.4622306157341054</v>
-      </c>
-      <c r="G57" t="n">
-        <v>29.14891464495499</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0.316923783293773</v>
-      </c>
-      <c r="I57" t="n">
-        <v>0.8492596743663299</v>
-      </c>
-      <c r="J57" t="n">
-        <v>9.345862087592849</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>induction_P_fold</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>BR04</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>0.8963766886448536</v>
-      </c>
-      <c r="D58" t="n">
-        <v>0.01849844643236161</v>
-      </c>
-      <c r="E58" t="n">
-        <v>0.001360318973264927</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0.0368825022641486</v>
-      </c>
-      <c r="G58" t="n">
-        <v>34.90224278706977</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0.03803921668782936</v>
-      </c>
-      <c r="I58" t="n">
-        <v>-114.6007574189448</v>
-      </c>
-      <c r="J58" t="n">
-        <v>-102.0664881662637</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>induction_P_fold</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>BR05</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>0.6900480364085393</v>
-      </c>
-      <c r="D59" t="n">
-        <v>0.02354891371535377</v>
-      </c>
-      <c r="E59" t="n">
-        <v>0.002084250644104035</v>
-      </c>
-      <c r="F59" t="n">
-        <v>0.04565359398890776</v>
-      </c>
-      <c r="G59" t="n">
-        <v>55.93598465298017</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0.1004445645283111</v>
-      </c>
-      <c r="I59" t="n">
-        <v>-105.6402637244324</v>
-      </c>
-      <c r="J59" t="n">
-        <v>-93.1059944717513</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>induction_P_fold</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>BR07</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>0.1707396630055101</v>
-      </c>
-      <c r="D60" t="n">
-        <v>0.08416859522791051</v>
-      </c>
-      <c r="E60" t="n">
-        <v>0.03534892528336719</v>
-      </c>
-      <c r="F60" t="n">
-        <v>0.1880130987015724</v>
-      </c>
-      <c r="G60" t="n">
-        <v>48.67700964922973</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0.279522348796704</v>
-      </c>
-      <c r="I60" t="n">
-        <v>-66.2471568102776</v>
-      </c>
-      <c r="J60" t="n">
-        <v>-50.69711441822565</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>induction_P_fold</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>BR08</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>-0.08254506559110553</v>
-      </c>
-      <c r="D61" t="n">
-        <v>0.1257882467589217</v>
-      </c>
-      <c r="E61" t="n">
-        <v>0.04088295963349029</v>
-      </c>
-      <c r="F61" t="n">
-        <v>0.2021953501777187</v>
-      </c>
-      <c r="G61" t="n">
-        <v>84.64490028401899</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0.7187631828415498</v>
-      </c>
-      <c r="I61" t="n">
-        <v>-55.92604844069487</v>
-      </c>
-      <c r="J61" t="n">
-        <v>-41.29953854227647</v>
+        <v>-58.10403318063636</v>
       </c>
     </row>
   </sheetData>
